--- a/AAII_Financials/Yearly/SLVYY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SLVYY_YR_FIN.xlsx
@@ -1119,10 +1119,10 @@
         <v>16</v>
       </c>
       <c r="D22" s="3">
-        <v>115100</v>
+        <v>116200</v>
       </c>
       <c r="E22" s="3">
-        <v>110800</v>
+        <v>111800</v>
       </c>
       <c r="F22" s="3">
         <v>71800</v>
